--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hubbly\Hubbly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{181595AA-1C94-4C63-8DF5-37BC4A3B3F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9707485E-8F81-4095-BD7E-28AD89CB8282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C5487672-C72A-44C9-9A1C-D8362D421C9E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Item</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>printify3d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link </t>
   </si>
 </sst>
 </file>
@@ -504,10 +507,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{111F8752-80A8-4F96-8E71-39877B4AFD33}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -517,8 +520,11 @@
       <c r="C1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -526,7 +532,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -534,7 +540,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -542,7 +548,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -550,7 +556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -558,7 +564,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -566,7 +572,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -574,7 +580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -585,18 +591,19 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
       <c r="B10">
         <v>0.1</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -609,7 +616,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C10" r:id="rId1" xr:uid="{48F1AD0F-FF3C-4F76-9143-0003FE215AEB}"/>
+    <hyperlink ref="D10" r:id="rId1" xr:uid="{48D0682D-F056-45C0-B860-81B7D3E7BCE1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hubbly\Hubbly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9707485E-8F81-4095-BD7E-28AD89CB8282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89005CC8-44C3-4200-932C-BAA7E62C9668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C5487672-C72A-44C9-9A1C-D8362D421C9E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Item</t>
   </si>
@@ -115,6 +115,27 @@
   </si>
   <si>
     <t xml:space="preserve">Link </t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC---SMD-SMT_Samsung-Electro-Mechanics-CL10A105KB8NNNC_C15849.html</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC---SMD-SMT_YAGEO-CC0603KRX7R9BB104_C14663.html</t>
+  </si>
+  <si>
+    <t>http://lcsc.com/product-detail/Chip-Resistor---Surface-Mount_UNI-ROYAL-0603WAF5101T5E_C23186.html</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Chip-Resistor---Surface-Mount_YAGEO-RC0603FR-07140KL_C185372.html</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/USB-HUB-Controllers_CoreChips-SL2-1s_C2684433.html</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Chip-Resistor---Surface-Mount_UNI-ROYAL-0603WAF1002T5E_C25804.html</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/USB-Connectors_SHOU-HAN-TYPE-C-16PIN-2MD-073-_C2765186.html</t>
   </si>
 </sst>
 </file>
@@ -531,6 +552,9 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -539,6 +563,9 @@
       <c r="C3" t="s">
         <v>13</v>
       </c>
+      <c r="D3" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -547,6 +574,9 @@
       <c r="C4" t="s">
         <v>14</v>
       </c>
+      <c r="D4" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -555,6 +585,9 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
+      <c r="D5" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -563,6 +596,9 @@
       <c r="C6" t="s">
         <v>19</v>
       </c>
+      <c r="D6" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -571,6 +607,9 @@
       <c r="C7" t="s">
         <v>16</v>
       </c>
+      <c r="D7" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -579,6 +618,9 @@
       <c r="C8" t="s">
         <v>17</v>
       </c>
+      <c r="D8" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -617,8 +659,15 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D10" r:id="rId1" xr:uid="{48D0682D-F056-45C0-B860-81B7D3E7BCE1}"/>
+    <hyperlink ref="D2" r:id="rId2" xr:uid="{915D79E7-8DC4-4C22-A92B-A68D95A54638}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{DC803AB1-E8BD-442B-A2F2-C2F342F5E3F7}"/>
+    <hyperlink ref="D4" r:id="rId4" xr:uid="{E00D0DC7-15F7-446F-AA9F-341504D9CECC}"/>
+    <hyperlink ref="D5" r:id="rId5" xr:uid="{0969EA17-BB7C-4D37-A488-5A3BBA95C2FA}"/>
+    <hyperlink ref="D6" r:id="rId6" xr:uid="{3DF35BA6-4950-446D-9CA8-94CB3E60024B}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{E469FFC2-BF32-4D81-96F2-271B1FC52648}"/>
+    <hyperlink ref="D7" r:id="rId8" xr:uid="{FDB6E27E-02ED-4354-8D17-68DB64B673E6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>